--- a/Материалы/dont-starve/Макеты/Банеры/Ключи кружки.xlsx
+++ b/Материалы/dont-starve/Макеты/Банеры/Ключи кружки.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
   <si>
     <t>Обложка_Уилсон</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game, Уилсон,  Wilson, персонажи don`t starve, ДСТ</t>
+  </si>
+  <si>
+    <t>Обложка_Персонажи_2</t>
   </si>
 </sst>
 </file>
@@ -1161,8 +1164,12 @@
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:2">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4"/>
+      <c r="A11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:2">
       <c r="A12" s="3"/>

--- a/Материалы/dont-starve/Макеты/Банеры/Ключи кружки.xlsx
+++ b/Материалы/dont-starve/Макеты/Банеры/Ключи кружки.xlsx
@@ -27,54 +27,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
-  <si>
-    <t>Обложка_Уилсон</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+  <si>
+    <t>Dont_Starve_Уилсон</t>
   </si>
   <si>
     <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game, Уилсон,  Wilson, ДСТ</t>
   </si>
   <si>
-    <t>Обложка_Уилсон_2</t>
-  </si>
-  <si>
-    <t>Обложка_Уилсон_3</t>
-  </si>
-  <si>
-    <t>Обложка_Уилсон_4</t>
-  </si>
-  <si>
-    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game, Уилсон,  Wilson, Pocket edition, ДСТ</t>
-  </si>
-  <si>
-    <t>Обложка_Максвелл</t>
-  </si>
-  <si>
-    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game,  Максвелл, Maxwell, ДСТ</t>
-  </si>
-  <si>
-    <t>Обложка_Verdant</t>
-  </si>
-  <si>
-    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game, Verdant, ДСТ</t>
-  </si>
-  <si>
-    <t>Обложка_Уилсон_5</t>
-  </si>
-  <si>
-    <t>Обложка_Уилсон_6</t>
-  </si>
-  <si>
-    <t>Обложка_Уилсон_7</t>
-  </si>
-  <si>
-    <t>Обложка_Персонажи_1</t>
-  </si>
-  <si>
-    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game, Уилсон,  Wilson, персонажи don`t starve, ДСТ</t>
-  </si>
-  <si>
-    <t>Обложка_Персонажи_2</t>
+    <t>Dont_Starve_Венди</t>
+  </si>
+  <si>
+    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game, Венди, Wendy, ДСТ</t>
+  </si>
+  <si>
+    <t>Dont_Starve_Венди_2</t>
+  </si>
+  <si>
+    <t>Dont_Starve_ Уиллоу</t>
+  </si>
+  <si>
+    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game,  Уиллоу, Willow, ДСТ</t>
+  </si>
+  <si>
+    <t>Dont_Starve_ Уиллоу_2</t>
+  </si>
+  <si>
+    <t>Dont_Starve_ Уиллоу_3</t>
+  </si>
+  <si>
+    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game,  Уиллоу, Willow, Уилсон, Wilson, ДСТ</t>
+  </si>
+  <si>
+    <t>Dont_Starve_Вуди</t>
+  </si>
+  <si>
+    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game, Вуди, Woodie, ДТС</t>
+  </si>
+  <si>
+    <t>Dont_Starve_Персонажи</t>
+  </si>
+  <si>
+    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game, персонажи don`t starve,ДТС</t>
+  </si>
+  <si>
+    <t>Dont_Starve_Персонажи_2</t>
+  </si>
+  <si>
+    <t>Dont_Starve_Циклоп-олень</t>
+  </si>
+  <si>
+    <t>Don't starve, Don't starve together, донт старв, донт старв тугезер, Не голодай, Не голодай вместе, Игра, Game, Циклоп-олень, Deerclops,ДТС</t>
   </si>
 </sst>
 </file>
@@ -1096,31 +1099,31 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:2">
       <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:2">
       <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:2">
@@ -1136,40 +1139,36 @@
         <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:2">
-      <c r="A11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="A11" s="3"/>
+      <c r="B11" s="4"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:2">
       <c r="A12" s="3"/>
